--- a/KURIKULUM2026_REVISI/009_PEDOMAN_CAPSTONE_PROJECT_DAN_TUGAS_AKHIR_NON_SKRIPSI.xlsx
+++ b/KURIKULUM2026_REVISI/009_PEDOMAN_CAPSTONE_PROJECT_DAN_TUGAS_AKHIR_NON_SKRIPSI.xlsx
@@ -185,16 +185,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -565,12 +565,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="69" customWidth="1" min="1" max="1"/>
-    <col width="24.15" customWidth="1" min="2" max="2"/>
-    <col width="37.95" customWidth="1" min="3" max="3"/>
+    <col width="69" customWidth="1" min="2" max="2"/>
+    <col width="69" customWidth="1" min="3" max="3"/>
     <col width="35.65" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -593,7 +593,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TAHAPAN SIKLUS CAPSTONE PROJECT FSTI</t>
+          <t>1.1 PEMENUHAN 7 KRITERIA CAPSTONE PROJECT APTIKOM</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -605,190 +605,277 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Minggu 1–3   : Pembentukan Tim, Identifikasi Masalah Mitra, &amp; Proposal Capstone.</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Kriteria Wajib APTIKOM SI v2.0</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Ketentuan Pelaksanaan `FST-610` di SISTEKIN</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Minggu 4–6   : Analisis Kebutuhan, Riset UX, &amp; Perancangan Arsitektur Sistem Cerdas.</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Menerapkan pengetahuan/keterampilan dari proses pembelajaran sebelumnya</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Prasyarat akademik: lulus `STI-506` Manajemen Proyek TI dan telah menempuh $\ge 100$ SKS. Mengintegrasikan capaian `STI-301` APSI, `STI-304` RPL, `STI-401` ML, `STI-407` Web Back End, dan MK peminatan.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Minggu 7–11  : Pengembangan Sistem (Sprint 1–3: Coding, AI Integration, Cloud Deploy).</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>**Dikerjakan secara berkelompok (3–6 orang)**</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>**Tim wajib berjumlah 3 (tiga) sampai 6 (enam) orang mahasiswa.** Komposisi tim disarankan lintas peminatan agar mencakup kompetensi AI/Data (P1), Cloud/Cyber (P2), dan Platform/UX (P3). Pembentukan tim dilakukan pada Minggu 1–3 dan disahkan oleh Koordinator Capstone.</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Minggu 12–13 : Pengujian Komprehensif (Unit Test, Usability Test, Security Testing).</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Menyelesaikan masalah riil/nyata di masyarakat</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Wajib bermitra dengan organisasi nyata (industri, UMKM, pemerintah daerah, sekolah, atau komunitas) yang dibuktikan dengan **surat kesediaan mitra**. Masalah bersumber dari kebutuhan mitra, bukan kasus hipotetis.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Minggu 14–16 : Capstone Expo / Demo Day, Uji Kelayakan Mitra, &amp; Laporan Akhir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>4 OPSI JALUR TUGAS AKHIR SISTEKIN 2026</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Opsi</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Jalur Tugas Akhir</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Luaran Wajib (Deliverables)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Target Profil Utama (PL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>**Termasuk kategori permasalahan infokom yang kompleks (*complex computing problem*)**</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Proyek wajib memenuhi **minimal 4 dari 7 atribut kompleksitas** pada §1.2. Dua atribut bersifat **wajib mutlak**: keterlibatan lebih dari satu pemangku kepentingan, dan kebutuhan/permasalahan yang belum terdefinisi dengan baik (*ill-defined requirements*). Verifikasi dilakukan saat sidang proposal Minggu 3.</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Luaran berupa desain (masalah skala besar) atau produk (masalah skala kecil)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Luaran wajib: (a) **produk sistem berfungsi** dengan TKT/TRL $\ge 5$ untuk masalah skala kecil–menengah; atau (b) **dokumen desain arsitektur lengkap** (SRS, SDD, ADR) untuk masalah berskala besar yang tidak dapat diselesaikan penuh dalam satu semester.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>**Jumlah SKS antara 3–6 SKS**</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>`FST-610` berbobot **3 SKS** (batas bawah rentang APTIKOM), setara 3 × 45 = 135 jam kegiatan belajar per semester sesuai Permendikbudristek No. 53/2023 Pasal 15.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>**Harus memiliki panduan tersendiri**</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Bagian §1 dokumen ini merupakan panduan normatif `FST-610`. Rubrik penilaian merujuk **Klaster Rubrik Proyek Rekayasa** pada Dokumen `018`, dan formula ketercapaian CPL merujuk Dokumen `008`.</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>✅ Terpenuhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>1.2 ATRIBUT *COMPLEX COMPUTING PROBLEM* (Kriteria Kelayakan Proposal)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Atribut Kompleksitas</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Indikator Verifikasi pada Sidang Proposal</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Sifat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Skripsi Riset</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Naskah Skripsi Ilmiah + Kode</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>• PL-1 (AI/Data Engineer)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="10" t="inlineStr"/>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Eksperimental</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Program Teruji + Uji Statistik</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>• PEO-3 (Studi Lanjut/Riset)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Proyek Inovasi</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Sistem Teruji Mitra (TRL ≥ 6) +</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>• PL-2 (Cloud/Cyber Integrator)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="10" t="inlineStr"/>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Produk Industri</t>
+          <t>**Keterlibatan lebih dari satu pemangku kepentingan**</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Laporan Teknis + Bukti HKI/Paten</t>
+          <t>Teridentifikasi $\ge 2$ kelompok pemangku kepentingan dengan kepentingan berbeda (mis. manajemen, operator, pelanggan akhir, regulator), didokumentasikan dalam *stakeholder map*.</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>• PL-3 (Platform Engineer)</t>
+          <t>**Wajib**</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>**Kebutuhan belum terdefinisi dengan baik (*ill-defined requirements*)**</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Kebutuhan awal mitra bersifat umum/ambigu sehingga tim harus melakukan elisitasi, riset pengguna, dan negosiasi ruang lingkup sebelum spesifikasi dapat dibakukan.</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>**Wajib**</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Tech Startup Mandiri</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Produk MVP Tervalidasi + Naskah</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>• PL-4 (Digital Technopreneur)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="10" t="inlineStr"/>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>(Technopreneur Track)</t>
+          <t>Tidak memiliki solusi baku yang dapat diterapkan langsung</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Pitch Deck + Bukti Traksi Pasar</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>• PEO-2 (Inovasi &amp; Wirausaha)</t>
+          <t>Solusi tidak tersedia sebagai produk siap pakai; memerlukan perancangan atau adaptasi arsitektur.</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Pilihan</t>
         </is>
       </c>
     </row>
@@ -798,179 +885,472 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Melibatkan integrasi lintas sistem, platform, atau sumber data</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Sistem berinteraksi dengan $\ge 2$ sistem/layanan eksternal (API, basis data legacy, perangkat IoT, layanan cloud).</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Pilihan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Memerlukan penerapan pengetahuan mendalam pada tingkat abstraksi tinggi</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Menuntut penguasaan konsep tingkat lanjut (model AI/ML, arsitektur terdistribusi, kriptografi terapan, orkestrasi kontainer).</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Pilihan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Memiliki batasan (*constraints*) non-teknis yang signifikan</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Terdapat kendala regulasi (UU PDP, SPBE), keamanan, aksesibilitas, anggaran, atau keberlanjutan yang memengaruhi keputusan desain.</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Pilihan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Menuntut pertimbangan dampak sosial, etis, atau keberlanjutan</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Solusi berdampak pada privasi data, kesetaraan akses, efisiensi sumber daya, atau keberlanjutan lingkungan (*environmental sustainability*).</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Pilihan</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TAHAPAN SIKLUS CAPSTONE PROJECT FSTI</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Minggu 1–3   : Pembentukan Tim (3–6 orang), Identifikasi Masalah Mitra, Sidang Proposal &amp; Verifikasi Kompleksitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 4–6   : Analisis Kebutuhan, Riset UX, &amp; Perancangan Arsitektur Sistem Cerdas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Minggu 7–11  : Pengembangan Sistem (Sprint 1–3: Coding, AI Integration, Cloud Deploy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Minggu 12–13 : Pengujian Komprehensif (Unit Test, Usability Test, Security Testing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Minggu 14–16 : Capstone Expo / Demo Day, Uji Kelayakan Mitra, &amp; Laporan Akhir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>4 OPSI JALUR TUGAS AKHIR SISTEKIN 2026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Opsi</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Jalur Tugas Akhir</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Luaran Wajib (Deliverables)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Target Profil Utama (PL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Skripsi Riset</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Naskah Skripsi Ilmiah + Kode</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>• PL-1 (AI/Data Engineer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="9" t="inlineStr"/>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Eksperimental</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Program Teruji + Uji Statistik</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>• PEO-3 (Studi Lanjut/Riset)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Proyek Inovasi</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Sistem Teruji Mitra (TRL ≥ 6) +</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>• PL-2 (Cloud/Cyber Integrator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="9" t="inlineStr"/>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Produk Industri</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Laporan Teknis + Bukti HKI/Paten</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>• PL-3 (Platform Engineer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Tech Startup Mandiri</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Produk MVP Tervalidasi + Naskah</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>• PL-4 (Digital Technopreneur)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="9" t="inlineStr"/>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>(Technopreneur Track)</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Pitch Deck + Bukti Traksi Pasar</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>• PEO-2 (Inovasi &amp; Wirausaha)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Publikasi Jurnal</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Artikel Terbit/Accepted di Jurnal</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>• Seluruh PL</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="10" t="inlineStr"/>
-      <c r="B19" s="8" t="inlineStr">
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="9" t="inlineStr"/>
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Ilmiah Bereputasi</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>SINTA 1/2 atau Scopus/WoS Q1-Q4</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>• PEO-3 (Akademisi/Riset)</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="40"/>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>RUBRIK ASESMEN SIDANG TUGAS AKHIR (6 SKS)</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Komponen Penilaian</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Bobot (%)</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>CPL yang Dinilai</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>1. Orisinalitas Gagasan &amp; Relevansi Visi SISTEKIN</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>KU1, P2</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>2. Kedalaman Metodologi &amp; Kebenaran Analisis Teknis</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>P1, P3, P4</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>3. Kualitas Produk / Luaran (Sistem, Model AI, MVP)</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>KK1 / KK2 / KK3 / KK5/ KK6</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>4. Sistematika Penulisan &amp; Kualitas Dokumentasi</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>KU2, S1</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>5. Performa Presentasi &amp; Kemampuan Mempertahankan</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>KU2, KU3</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>TOTAL SKOR</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>**100%**</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>Kelulusan: Nilai ≥ 65 (B)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/KURIKULUM2026_REVISI/009_PEDOMAN_CAPSTONE_PROJECT_DAN_TUGAS_AKHIR_NON_SKRIPSI.xlsx
+++ b/KURIKULUM2026_REVISI/009_PEDOMAN_CAPSTONE_PROJECT_DAN_TUGAS_AKHIR_NON_SKRIPSI.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Prasyarat akademik: lulus `STI-506` Manajemen Proyek TI dan telah menempuh $\ge 100$ SKS. Mengintegrasikan capaian `STI-301` APSI, `STI-304` RPL, `STI-401` ML, `STI-407` Web Back End, dan MK peminatan.</t>
+          <t>Prasyarat akademik: lulus `STI-523` Manajemen Proyek TI dan telah menempuh $\ge 100$ SKS. Mengintegrasikan capaian `STI-306` APSI, `STI-309` RPL, `STI-413` ML, `STI-416` Web Back End, dan MK peminatan.</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
